--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,109 +1304,1439 @@
           <t>12:43:14</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>115030924</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="B13" t="n">
+        <v>115030924</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" t="n">
+        <v>18</v>
+      </c>
+      <c r="I13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26</v>
+      </c>
+      <c r="M13" t="n">
+        <v>34</v>
+      </c>
+      <c r="N13" t="n">
+        <v>36</v>
+      </c>
+      <c r="O13" t="n">
+        <v>40</v>
+      </c>
+      <c r="P13" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>46</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>54</v>
+      </c>
+      <c r="T13" t="n">
+        <v>64</v>
+      </c>
+      <c r="U13" t="n">
+        <v>65</v>
+      </c>
+      <c r="V13" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12:48:18</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>115030925</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="n">
+        <v>27</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K14" t="n">
+        <v>43</v>
+      </c>
+      <c r="L14" t="n">
+        <v>44</v>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="n">
+        <v>52</v>
+      </c>
+      <c r="O14" t="n">
+        <v>58</v>
+      </c>
+      <c r="P14" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>64</v>
+      </c>
+      <c r="R14" t="n">
+        <v>66</v>
+      </c>
+      <c r="S14" t="n">
+        <v>68</v>
+      </c>
+      <c r="T14" t="n">
+        <v>72</v>
+      </c>
+      <c r="U14" t="n">
+        <v>77</v>
+      </c>
+      <c r="V14" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12:53:22</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>115030926</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H15" t="n">
+        <v>26</v>
+      </c>
+      <c r="I15" t="n">
+        <v>29</v>
+      </c>
+      <c r="J15" t="n">
+        <v>42</v>
+      </c>
+      <c r="K15" t="n">
+        <v>43</v>
+      </c>
+      <c r="L15" t="n">
+        <v>45</v>
+      </c>
+      <c r="M15" t="n">
+        <v>52</v>
+      </c>
+      <c r="N15" t="n">
+        <v>53</v>
+      </c>
+      <c r="O15" t="n">
+        <v>55</v>
+      </c>
+      <c r="P15" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>59</v>
+      </c>
+      <c r="R15" t="n">
+        <v>68</v>
+      </c>
+      <c r="S15" t="n">
+        <v>70</v>
+      </c>
+      <c r="T15" t="n">
+        <v>74</v>
+      </c>
+      <c r="U15" t="n">
+        <v>76</v>
+      </c>
+      <c r="V15" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12:58:25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>115030927</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21</v>
+      </c>
+      <c r="I16" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" t="n">
+        <v>40</v>
+      </c>
+      <c r="K16" t="n">
+        <v>47</v>
+      </c>
+      <c r="L16" t="n">
+        <v>49</v>
+      </c>
+      <c r="M16" t="n">
+        <v>50</v>
+      </c>
+      <c r="N16" t="n">
+        <v>51</v>
+      </c>
+      <c r="O16" t="n">
+        <v>54</v>
+      </c>
+      <c r="P16" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>63</v>
+      </c>
+      <c r="R16" t="n">
+        <v>64</v>
+      </c>
+      <c r="S16" t="n">
+        <v>66</v>
+      </c>
+      <c r="T16" t="n">
+        <v>67</v>
+      </c>
+      <c r="U16" t="n">
+        <v>71</v>
+      </c>
+      <c r="V16" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>13:03:29</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>115030928</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J17" t="n">
+        <v>33</v>
+      </c>
+      <c r="K17" t="n">
+        <v>35</v>
+      </c>
+      <c r="L17" t="n">
+        <v>36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>37</v>
+      </c>
+      <c r="N17" t="n">
+        <v>45</v>
+      </c>
+      <c r="O17" t="n">
+        <v>55</v>
+      </c>
+      <c r="P17" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>62</v>
+      </c>
+      <c r="R17" t="n">
+        <v>67</v>
+      </c>
+      <c r="S17" t="n">
+        <v>74</v>
+      </c>
+      <c r="T17" t="n">
+        <v>75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>76</v>
+      </c>
+      <c r="V17" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>13:08:33</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>115030929</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" t="n">
+        <v>22</v>
+      </c>
+      <c r="F18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G18" t="n">
+        <v>26</v>
+      </c>
+      <c r="H18" t="n">
+        <v>31</v>
+      </c>
+      <c r="I18" t="n">
+        <v>36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>37</v>
+      </c>
+      <c r="K18" t="n">
+        <v>38</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39</v>
+      </c>
+      <c r="M18" t="n">
+        <v>41</v>
+      </c>
+      <c r="N18" t="n">
+        <v>45</v>
+      </c>
+      <c r="O18" t="n">
+        <v>47</v>
+      </c>
+      <c r="P18" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>55</v>
+      </c>
+      <c r="R18" t="n">
+        <v>58</v>
+      </c>
+      <c r="S18" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" t="n">
+        <v>74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>13:14:37</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>115030930</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21</v>
+      </c>
+      <c r="G19" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" t="n">
+        <v>25</v>
+      </c>
+      <c r="I19" t="n">
+        <v>27</v>
+      </c>
+      <c r="J19" t="n">
+        <v>28</v>
+      </c>
+      <c r="K19" t="n">
+        <v>29</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33</v>
+      </c>
+      <c r="M19" t="n">
+        <v>37</v>
+      </c>
+      <c r="N19" t="n">
+        <v>38</v>
+      </c>
+      <c r="O19" t="n">
+        <v>42</v>
+      </c>
+      <c r="P19" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>46</v>
+      </c>
+      <c r="R19" t="n">
+        <v>51</v>
+      </c>
+      <c r="S19" t="n">
+        <v>61</v>
+      </c>
+      <c r="T19" t="n">
+        <v>62</v>
+      </c>
+      <c r="U19" t="n">
+        <v>68</v>
+      </c>
+      <c r="V19" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>13:18:40</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>115030931</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" t="n">
+        <v>23</v>
+      </c>
+      <c r="H20" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" t="n">
+        <v>26</v>
+      </c>
+      <c r="J20" t="n">
+        <v>31</v>
+      </c>
+      <c r="K20" t="n">
+        <v>35</v>
+      </c>
+      <c r="L20" t="n">
+        <v>39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>43</v>
+      </c>
+      <c r="N20" t="n">
+        <v>52</v>
+      </c>
+      <c r="O20" t="n">
+        <v>55</v>
+      </c>
+      <c r="P20" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>57</v>
+      </c>
+      <c r="R20" t="n">
+        <v>66</v>
+      </c>
+      <c r="S20" t="n">
+        <v>71</v>
+      </c>
+      <c r="T20" t="n">
+        <v>73</v>
+      </c>
+      <c r="U20" t="n">
+        <v>75</v>
+      </c>
+      <c r="V20" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>13:22:43</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>115030932</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>29</v>
+      </c>
+      <c r="J21" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" t="n">
+        <v>35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36</v>
+      </c>
+      <c r="M21" t="n">
+        <v>39</v>
+      </c>
+      <c r="N21" t="n">
+        <v>42</v>
+      </c>
+      <c r="O21" t="n">
+        <v>48</v>
+      </c>
+      <c r="P21" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>55</v>
+      </c>
+      <c r="R21" t="n">
+        <v>56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>62</v>
+      </c>
+      <c r="T21" t="n">
+        <v>64</v>
+      </c>
+      <c r="U21" t="n">
+        <v>71</v>
+      </c>
+      <c r="V21" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>13:27:46</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>115030933</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11</v>
+      </c>
+      <c r="E22" t="n">
+        <v>14</v>
+      </c>
+      <c r="F22" t="n">
+        <v>19</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>27</v>
+      </c>
+      <c r="I22" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" t="n">
+        <v>31</v>
+      </c>
+      <c r="K22" t="n">
+        <v>35</v>
+      </c>
+      <c r="L22" t="n">
+        <v>38</v>
+      </c>
+      <c r="M22" t="n">
+        <v>43</v>
+      </c>
+      <c r="N22" t="n">
+        <v>47</v>
+      </c>
+      <c r="O22" t="n">
+        <v>48</v>
+      </c>
+      <c r="P22" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>58</v>
+      </c>
+      <c r="S22" t="n">
+        <v>63</v>
+      </c>
+      <c r="T22" t="n">
+        <v>75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>79</v>
+      </c>
+      <c r="V22" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>13:32:50</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>115030934</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19</v>
+      </c>
+      <c r="H23" t="n">
+        <v>23</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27</v>
+      </c>
+      <c r="J23" t="n">
+        <v>33</v>
+      </c>
+      <c r="K23" t="n">
+        <v>36</v>
+      </c>
+      <c r="L23" t="n">
+        <v>44</v>
+      </c>
+      <c r="M23" t="n">
+        <v>45</v>
+      </c>
+      <c r="N23" t="n">
+        <v>52</v>
+      </c>
+      <c r="O23" t="n">
+        <v>57</v>
+      </c>
+      <c r="P23" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>62</v>
+      </c>
+      <c r="R23" t="n">
+        <v>63</v>
+      </c>
+      <c r="S23" t="n">
+        <v>72</v>
+      </c>
+      <c r="T23" t="n">
+        <v>73</v>
+      </c>
+      <c r="U23" t="n">
+        <v>77</v>
+      </c>
+      <c r="V23" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>13:37:53</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>115030935</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" t="n">
+        <v>25</v>
+      </c>
+      <c r="J24" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" t="n">
+        <v>34</v>
+      </c>
+      <c r="L24" t="n">
+        <v>45</v>
+      </c>
+      <c r="M24" t="n">
+        <v>47</v>
+      </c>
+      <c r="N24" t="n">
+        <v>50</v>
+      </c>
+      <c r="O24" t="n">
+        <v>51</v>
+      </c>
+      <c r="P24" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>55</v>
+      </c>
+      <c r="R24" t="n">
+        <v>63</v>
+      </c>
+      <c r="S24" t="n">
+        <v>66</v>
+      </c>
+      <c r="T24" t="n">
+        <v>67</v>
+      </c>
+      <c r="U24" t="n">
+        <v>75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>13:42:57</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>115030936</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="n">
+        <v>21</v>
+      </c>
+      <c r="G25" t="n">
+        <v>23</v>
+      </c>
+      <c r="H25" t="n">
+        <v>24</v>
+      </c>
+      <c r="I25" t="n">
+        <v>29</v>
+      </c>
+      <c r="J25" t="n">
+        <v>31</v>
+      </c>
+      <c r="K25" t="n">
+        <v>34</v>
+      </c>
+      <c r="L25" t="n">
+        <v>36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>38</v>
+      </c>
+      <c r="N25" t="n">
+        <v>55</v>
+      </c>
+      <c r="O25" t="n">
+        <v>57</v>
+      </c>
+      <c r="P25" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>66</v>
+      </c>
+      <c r="R25" t="n">
+        <v>67</v>
+      </c>
+      <c r="S25" t="n">
+        <v>68</v>
+      </c>
+      <c r="T25" t="n">
+        <v>69</v>
+      </c>
+      <c r="U25" t="n">
+        <v>71</v>
+      </c>
+      <c r="V25" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>13:48:00</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>115030937</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>14</v>
+      </c>
+      <c r="F26" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" t="n">
+        <v>19</v>
+      </c>
+      <c r="H26" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" t="n">
+        <v>26</v>
+      </c>
+      <c r="J26" t="n">
+        <v>30</v>
+      </c>
+      <c r="K26" t="n">
+        <v>31</v>
+      </c>
+      <c r="L26" t="n">
+        <v>34</v>
+      </c>
+      <c r="M26" t="n">
+        <v>35</v>
+      </c>
+      <c r="N26" t="n">
+        <v>36</v>
+      </c>
+      <c r="O26" t="n">
+        <v>37</v>
+      </c>
+      <c r="P26" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>43</v>
+      </c>
+      <c r="R26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>54</v>
+      </c>
+      <c r="T26" t="n">
+        <v>59</v>
+      </c>
+      <c r="U26" t="n">
+        <v>61</v>
+      </c>
+      <c r="V26" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>13:54:05</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>115030938</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>17</v>
+      </c>
+      <c r="I27" t="n">
+        <v>22</v>
+      </c>
+      <c r="J27" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" t="n">
+        <v>32</v>
+      </c>
+      <c r="L27" t="n">
+        <v>34</v>
+      </c>
+      <c r="M27" t="n">
+        <v>43</v>
+      </c>
+      <c r="N27" t="n">
+        <v>45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>49</v>
+      </c>
+      <c r="P27" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>56</v>
+      </c>
+      <c r="R27" t="n">
+        <v>57</v>
+      </c>
+      <c r="S27" t="n">
+        <v>64</v>
+      </c>
+      <c r="T27" t="n">
+        <v>66</v>
+      </c>
+      <c r="U27" t="n">
+        <v>71</v>
+      </c>
+      <c r="V27" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>13:59:08</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>115030939</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>17</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>27</v>
+      </c>
+      <c r="I28" t="n">
+        <v>31</v>
+      </c>
+      <c r="J28" t="n">
+        <v>32</v>
+      </c>
+      <c r="K28" t="n">
+        <v>37</v>
+      </c>
+      <c r="L28" t="n">
+        <v>40</v>
+      </c>
+      <c r="M28" t="n">
+        <v>44</v>
+      </c>
+      <c r="N28" t="n">
+        <v>45</v>
+      </c>
+      <c r="O28" t="n">
+        <v>47</v>
+      </c>
+      <c r="P28" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>55</v>
+      </c>
+      <c r="R28" t="n">
+        <v>63</v>
+      </c>
+      <c r="S28" t="n">
+        <v>72</v>
+      </c>
+      <c r="T28" t="n">
+        <v>77</v>
+      </c>
+      <c r="U28" t="n">
+        <v>78</v>
+      </c>
+      <c r="V28" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14:04:12</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>115030940</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>19</v>
+      </c>
+      <c r="G29" t="n">
+        <v>22</v>
+      </c>
+      <c r="H29" t="n">
+        <v>23</v>
+      </c>
+      <c r="I29" t="n">
+        <v>27</v>
+      </c>
+      <c r="J29" t="n">
+        <v>32</v>
+      </c>
+      <c r="K29" t="n">
+        <v>33</v>
+      </c>
+      <c r="L29" t="n">
+        <v>36</v>
+      </c>
+      <c r="M29" t="n">
+        <v>37</v>
+      </c>
+      <c r="N29" t="n">
+        <v>39</v>
+      </c>
+      <c r="O29" t="n">
+        <v>40</v>
+      </c>
+      <c r="P29" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>45</v>
+      </c>
+      <c r="R29" t="n">
+        <v>52</v>
+      </c>
+      <c r="S29" t="n">
+        <v>55</v>
+      </c>
+      <c r="T29" t="n">
+        <v>56</v>
+      </c>
+      <c r="U29" t="n">
+        <v>64</v>
+      </c>
+      <c r="V29" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14:08:14</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>115030941</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16</v>
+      </c>
+      <c r="I30" t="n">
+        <v>24</v>
+      </c>
+      <c r="J30" t="n">
+        <v>27</v>
+      </c>
+      <c r="K30" t="n">
+        <v>30</v>
+      </c>
+      <c r="L30" t="n">
+        <v>32</v>
+      </c>
+      <c r="M30" t="n">
+        <v>37</v>
+      </c>
+      <c r="N30" t="n">
+        <v>41</v>
+      </c>
+      <c r="O30" t="n">
+        <v>42</v>
+      </c>
+      <c r="P30" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>56</v>
+      </c>
+      <c r="R30" t="n">
+        <v>57</v>
+      </c>
+      <c r="S30" t="n">
+        <v>61</v>
+      </c>
+      <c r="T30" t="n">
+        <v>62</v>
+      </c>
+      <c r="U30" t="n">
+        <v>67</v>
+      </c>
+      <c r="V30" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14:13:18</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>115030942</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I31" t="n">
+        <v>14</v>
+      </c>
+      <c r="J31" t="n">
+        <v>16</v>
+      </c>
+      <c r="K31" t="n">
+        <v>24</v>
+      </c>
+      <c r="L31" t="n">
+        <v>27</v>
+      </c>
+      <c r="M31" t="n">
+        <v>28</v>
+      </c>
+      <c r="N31" t="n">
+        <v>29</v>
+      </c>
+      <c r="O31" t="n">
+        <v>34</v>
+      </c>
+      <c r="P31" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>45</v>
+      </c>
+      <c r="R31" t="n">
+        <v>51</v>
+      </c>
+      <c r="S31" t="n">
+        <v>60</v>
+      </c>
+      <c r="T31" t="n">
+        <v>61</v>
+      </c>
+      <c r="U31" t="n">
+        <v>75</v>
+      </c>
+      <c r="V31" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14:18:22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>115030943</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>67</t>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>79</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2634,107 +2634,247 @@
           <t>14:18:22</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>115030943</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
+      <c r="B32" t="n">
+        <v>115030943</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>21</v>
+      </c>
+      <c r="H32" t="n">
+        <v>25</v>
+      </c>
+      <c r="I32" t="n">
+        <v>32</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34</v>
+      </c>
+      <c r="K32" t="n">
+        <v>36</v>
+      </c>
+      <c r="L32" t="n">
+        <v>40</v>
+      </c>
+      <c r="M32" t="n">
+        <v>42</v>
+      </c>
+      <c r="N32" t="n">
+        <v>43</v>
+      </c>
+      <c r="O32" t="n">
+        <v>50</v>
+      </c>
+      <c r="P32" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>61</v>
+      </c>
+      <c r="R32" t="n">
+        <v>64</v>
+      </c>
+      <c r="S32" t="n">
+        <v>71</v>
+      </c>
+      <c r="T32" t="n">
+        <v>74</v>
+      </c>
+      <c r="U32" t="n">
+        <v>77</v>
+      </c>
+      <c r="V32" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14:22:25</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>115030944</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12</v>
+      </c>
+      <c r="G33" t="n">
+        <v>18</v>
+      </c>
+      <c r="H33" t="n">
+        <v>19</v>
+      </c>
+      <c r="I33" t="n">
+        <v>21</v>
+      </c>
+      <c r="J33" t="n">
+        <v>26</v>
+      </c>
+      <c r="K33" t="n">
+        <v>29</v>
+      </c>
+      <c r="L33" t="n">
+        <v>30</v>
+      </c>
+      <c r="M33" t="n">
+        <v>32</v>
+      </c>
+      <c r="N33" t="n">
+        <v>35</v>
+      </c>
+      <c r="O33" t="n">
+        <v>37</v>
+      </c>
+      <c r="P33" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>44</v>
+      </c>
+      <c r="R33" t="n">
+        <v>47</v>
+      </c>
+      <c r="S33" t="n">
+        <v>56</v>
+      </c>
+      <c r="T33" t="n">
+        <v>63</v>
+      </c>
+      <c r="U33" t="n">
+        <v>70</v>
+      </c>
+      <c r="V33" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14:27:28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>115030945</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
         <is>
           <t>79</t>
         </is>
